--- a/restaurants_info.xlsx
+++ b/restaurants_info.xlsx
@@ -19,7 +19,7 @@
     <t>pizza360metrovile@gmail.com</t>
   </si>
   <si>
-    <t>jskaohsbxusi425</t>
+    <t>2Pizza_360_com</t>
   </si>
 </sst>
 </file>
@@ -39,7 +39,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -56,6 +56,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF93C47D"/>
         <bgColor rgb="FF93C47D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -76,6 +82,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -305,6 +314,9 @@
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="G1" s="4">
+        <v>3.13088136E9</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
